--- a/output/pdf_financials_xlsx/MOON.xlsx
+++ b/output/pdf_financials_xlsx/MOON.xlsx
@@ -1114,40 +1114,40 @@
         <v>-0.133862</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.526381</v>
+        <v>-0.526381</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.526261</v>
+        <v>-1.526261</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.739733</v>
+        <v>-0.739733</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.423759</v>
+        <v>-1.423759</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.257153</v>
+        <v>-0.257153</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.263337</v>
+        <v>-0.263337</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.520121</v>
+        <v>-1.520121</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.349084</v>
+        <v>-0.349084</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.340856</v>
+        <v>-0.340856</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>38.77286</v>
+        <v>-38.77286</v>
       </c>
     </row>
     <row r="17">
@@ -1350,40 +1350,40 @@
         <v>-0.133862</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.526381</v>
+        <v>-0.526381</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.526261</v>
+        <v>-1.526261</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.739733</v>
+        <v>-0.739733</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.423759</v>
+        <v>-1.423759</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.257153</v>
+        <v>-0.257153</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.263337</v>
+        <v>-0.263337</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.520121</v>
+        <v>-1.520121</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.349084</v>
+        <v>-0.349084</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.340856</v>
+        <v>-0.340856</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>38.77286</v>
+        <v>-38.77286</v>
       </c>
     </row>
     <row r="21">
@@ -1488,40 +1488,40 @@
         <v>-0.133862</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.526381</v>
+        <v>-0.526381</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.526261</v>
+        <v>-1.526261</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.739733</v>
+        <v>-0.739733</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.423759</v>
+        <v>-1.423759</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.257153</v>
+        <v>-0.257153</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.263337</v>
+        <v>-0.263337</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.520121</v>
+        <v>-1.520121</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.349084</v>
+        <v>-0.349084</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.340856</v>
+        <v>-0.340856</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>38.77286</v>
+        <v>-38.77286</v>
       </c>
     </row>
     <row r="24">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>69.3755</v>
+        <v>-69.3755</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>2.13035</v>
+        <v>-2.13035</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>3.541114</v>
+        <v>-3.541114</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -1700,40 +1700,40 @@
         <v>-0.133862</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.526381</v>
+        <v>-0.526381</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.526261</v>
+        <v>-1.526261</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.739733</v>
+        <v>-0.739733</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.423759</v>
+        <v>-1.423759</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.257153</v>
+        <v>-0.257153</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.263337</v>
+        <v>-0.263337</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.520121</v>
+        <v>-1.520121</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.349084</v>
+        <v>-0.349084</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.340856</v>
+        <v>-0.340856</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>38.77286</v>
+        <v>-38.77286</v>
       </c>
     </row>
     <row r="28">
@@ -1792,40 +1792,40 @@
         <v>-0.133862</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.526381</v>
+        <v>-0.526381</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.526261</v>
+        <v>-1.526261</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.739733</v>
+        <v>-0.739733</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.423759</v>
+        <v>-1.423759</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.257153</v>
+        <v>-0.257153</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.263337</v>
+        <v>-0.263337</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.520121</v>
+        <v>-1.520121</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.349084</v>
+        <v>-0.349084</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.340856</v>
+        <v>-0.340856</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>40.204582</v>
+        <v>-37.341138</v>
       </c>
     </row>
     <row r="30">
@@ -1910,40 +1910,40 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -30701,10 +30701,10 @@
         </is>
       </c>
       <c r="P299" s="5" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="Q299" s="5" t="n">
-        <v>38.77286</v>
+        <v>-38.77286</v>
       </c>
     </row>
     <row r="300">
@@ -30948,10 +30948,10 @@
         </is>
       </c>
       <c r="P302" s="5" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="Q302" s="5" t="n">
-        <v>38.77286</v>
+        <v>-38.77286</v>
       </c>
     </row>
     <row r="303">
@@ -31941,31 +31941,31 @@
         </is>
       </c>
       <c r="H315" s="5" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="I315" s="5" t="n">
-        <v>0.739733</v>
+        <v>-0.739733</v>
       </c>
       <c r="J315" s="5" t="n">
-        <v>1.423759</v>
+        <v>-1.423759</v>
       </c>
       <c r="K315" s="5" t="n">
-        <v>0.257153</v>
+        <v>-0.257153</v>
       </c>
       <c r="L315" s="5" t="n">
-        <v>0.263337</v>
+        <v>-0.263337</v>
       </c>
       <c r="M315" s="5" t="n">
-        <v>1.520121</v>
+        <v>-1.520121</v>
       </c>
       <c r="N315" s="5" t="n">
-        <v>0.349084</v>
+        <v>-0.349084</v>
       </c>
       <c r="O315" s="5" t="n">
-        <v>0.340856</v>
+        <v>-0.340856</v>
       </c>
       <c r="P315" s="5" t="n">
-        <v>0.495756</v>
+        <v>-0.495756</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -34520,13 +34520,13 @@
         </is>
       </c>
       <c r="F348" s="5" t="n">
-        <v>0.526381</v>
+        <v>-0.526381</v>
       </c>
       <c r="G348" s="5" t="n">
-        <v>1.526261</v>
+        <v>-1.526261</v>
       </c>
       <c r="H348" s="5" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -34836,13 +34836,13 @@
         </is>
       </c>
       <c r="F352" s="5" t="n">
-        <v>0.526381</v>
+        <v>-0.526381</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>1.526261</v>
+        <v>-1.526261</v>
       </c>
       <c r="H352" s="5" t="n">
-        <v>0.246379</v>
+        <v>-0.246379</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MOON.xlsx
+++ b/output/pdf_financials_xlsx/MOON.xlsx
@@ -957,13 +957,13 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001742</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037809</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.961843</v>
       </c>
     </row>
     <row r="13">
@@ -1727,13 +1727,13 @@
         <v>-0.349084</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.340856</v>
+        <v>-0.339114</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.495756</v>
+        <v>-0.457947</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-38.77286</v>
+        <v>-37.811017</v>
       </c>
     </row>
     <row r="28">
@@ -1819,13 +1819,13 @@
         <v>-0.349084</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.340856</v>
+        <v>-0.339114</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.495756</v>
+        <v>-0.457947</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-37.341138</v>
+        <v>-36.379295</v>
       </c>
     </row>
     <row r="30">
@@ -2032,37 +2032,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.819508</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.497568</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.200187</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.113814</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.308701</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.023053</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.095927</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.267015</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.582073</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.030193</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.355343</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>3.00172</v>
@@ -2124,37 +2124,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.819508</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.497568</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.200187</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.113814</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.308701</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.023053</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.095927</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.267015</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.582073</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.030193</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.355343</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>3.46922</v>
@@ -2676,37 +2676,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.826346</v>
+        <v>0.006838</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.505538</v>
+        <v>0.00797</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.214814</v>
+        <v>0.014627</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.128004</v>
+        <v>0.01419</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.320841</v>
+        <v>0.01214</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06758500000000001</v>
+        <v>0.044532</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.115236</v>
+        <v>0.019309</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.290054</v>
+        <v>0.023039</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.723567</v>
+        <v>0.141494</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.056991</v>
+        <v>0.026798</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.37838</v>
+        <v>0.023037</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>27.675289</v>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -30154,7 +30154,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -30318,7 +30318,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -31839,7 +31839,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -32516,7 +32516,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">

--- a/output/pdf_financials_xlsx/MOON.xlsx
+++ b/output/pdf_financials_xlsx/MOON.xlsx
@@ -3512,13 +3512,13 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.019418</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.400891</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>4.248711</v>
       </c>
     </row>
     <row r="65">
@@ -3650,13 +3650,13 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.5018089999999999</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>8.042469000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>1.199391</v>
       </c>
     </row>
     <row r="111">
@@ -5709,13 +5709,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003022</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003022</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -14514,7 +14514,11 @@
           <t>Interest and accretion expense</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -20327,7 +20331,11 @@
           <t>Private placement 5b 2,852,702 1,621,075 285,271</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -21425,7 +21433,11 @@
           <t>Private placement 5b 8,589,557 257,686 42,948</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -21913,7 +21925,11 @@
           <t>Private placement 5b 28,527,017 1,621,075 285,271</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -22962,7 +22978,11 @@
           <t>Private placement 5b 8,589,557 257,686 42,948</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -28195,7 +28215,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E268" s="5" t="n">
         <v>-0.0007</v>
       </c>
